--- a/public/order-template.xlsx
+++ b/public/order-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Worksheet" state="visible" r:id="rId4"/>
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>닥터비트 온라인몰 자재 출고 신청서</t>
   </si>
   <si>
-    <t>기준일: 2026-06-26 ~ 2026-06-29</t>
+    <t>기준일: 2026-06-30 ~ 2026-06-30</t>
+  </si>
+  <si>
+    <t>창고코드</t>
+  </si>
+  <si>
+    <t>장소코드</t>
   </si>
   <si>
     <t>출고일자</t>
@@ -34,6 +40,15 @@
     <t>거래처명</t>
   </si>
   <si>
+    <t>거래구분</t>
+  </si>
+  <si>
+    <t>과세구분</t>
+  </si>
+  <si>
+    <t>단가구분</t>
+  </si>
+  <si>
     <t>품번</t>
   </si>
   <si>
@@ -76,7 +91,16 @@
     <t>배송처</t>
   </si>
   <si>
-    <t>합계</t>
+    <t>환종</t>
+  </si>
+  <si>
+    <t>환율</t>
+  </si>
+  <si>
+    <t>프로젝트코드</t>
+  </si>
+  <si>
+    <t>재고수량</t>
   </si>
 </sst>
 </file>
@@ -127,7 +151,7 @@
       <name val="맑은 고딕"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,8 +160,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFABCDEF"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -204,12 +240,21 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -218,6 +263,9 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -535,30 +583,34 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="12.5703125" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.42578125" style="1" customWidth="1"/>
-    <col min="7" max="11" width="12.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="12.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="35" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21" style="1" customWidth="1"/>
-    <col min="18" max="18" width="107.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.140625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="45.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16" width="12.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" style="1" customWidth="1"/>
+    <col min="18" max="19" width="12.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="35" style="1" customWidth="1"/>
+    <col min="22" max="22" width="21" style="1" customWidth="1"/>
+    <col min="23" max="23" width="56.5703125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" customWidth="1"/>
+    <col min="25" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="17.140625" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="37.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="37.5" customHeight="1" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -574,13 +626,16 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
-    </row>
-    <row r="2" ht="23.25" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+    </row>
+    <row r="2" ht="23.25" customHeight="1" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -596,319 +651,416 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-    </row>
-    <row r="3" ht="69" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="20.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="20.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="20.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="20.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R8" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="S8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="16"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="16"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" ref="G12:N12" si="0">G5+G6+G7+G8+G9+G10+G11</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-    </row>
-    <row r="13" ht="19.5" customHeight="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-    </row>
-    <row r="15" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="16"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
+      <c r="AA12" s="16"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="16"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
+      <c r="AA14" s="16"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="16"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="C1:W1"/>
+    <mergeCell ref="C2:W2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="37" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
